--- a/data/trans_orig/SE_ADU-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/SE_ADU-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2007</t>
+          <t>Sexo adulto elegido en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1313158</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1315113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1268470</t>
+          <t>1270291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1360666</t>
+          <t>1361093</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -846,82 +846,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1029816</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>1031723</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1038</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1031723</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>986169</t>
+          <t>985742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1078365</t>
+          <t>1076544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,47 +1111,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1585712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>1587673</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1554</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1587673</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1532601</t>
+          <t>1529902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1642797</t>
+          <t>1642952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,82 +1189,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1691442</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1649</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>1693413</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1649</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1693413</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1638289</t>
+          <t>1638134</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1748485</t>
+          <t>1751184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,47 +1454,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>474393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>476412</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>476412</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>445445</t>
+          <t>442829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>510671</t>
+          <t>508772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -1532,82 +1532,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>549403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>551408</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>551408</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517149</t>
+          <t>519048</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582375</t>
+          <t>584991</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,92%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,47 +1797,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3377229</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>3379197</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3379197</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3299203</t>
+          <t>3299502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3468302</t>
+          <t>3461675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3274586</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3276543</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3187439</t>
+          <t>3194066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3356538</t>
+          <t>3356239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2012</t>
+          <t>Sexo adulto elegido en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,47 +2371,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1335738</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>1337797</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1247</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1337797</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1288696</t>
+          <t>1287723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1386367</t>
+          <t>1387762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -2449,82 +2449,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>972584</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>974643</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>974643</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>926073</t>
+          <t>924678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1023744</t>
+          <t>1024717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,47 +2714,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1755740</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1635</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>1757803</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1635</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1757803</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1685392</t>
+          <t>1697545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1819559</t>
+          <t>1827484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -2792,82 +2792,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1961926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>1963957</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1963957</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1902201</t>
+          <t>1894276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2036368</t>
+          <t>2024215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,47 +3057,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>456499</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>458631</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>458631</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>424153</t>
+          <t>429091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>492553</t>
+          <t>491266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>447260</t>
+          <t>448547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>515660</t>
+          <t>510722</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,47 +3400,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3552158</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>3554230</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3554230</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3468971</t>
+          <t>3465078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3641699</t>
+          <t>3645944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -3478,82 +3478,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3417731</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>3419782</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3202</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3419782</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3332313</t>
+          <t>3328068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3505041</t>
+          <t>3508934</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,31%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2016</t>
+          <t>Sexo adulto elegido en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,47 +3974,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>992521</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>994660</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>994660</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>955455</t>
+          <t>950138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1036575</t>
+          <t>1033460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,09%</t>
         </is>
       </c>
     </row>
@@ -4052,82 +4052,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>752449</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>754347</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2139</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>754347</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712432</t>
+          <t>715547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>793552</t>
+          <t>798869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,47 +4317,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1986300</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>1988300</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1908</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1988300</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1922369</t>
+          <t>1922389</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2053631</t>
+          <t>2052613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -4395,82 +4395,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2074343</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>2076385</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2076385</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2011054</t>
+          <t>2012072</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2142316</t>
+          <t>2142296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>547139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>549140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>517018</t>
+          <t>515796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>581793</t>
+          <t>581377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -4738,82 +4738,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>544794</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>546886</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>546886</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>514234</t>
+          <t>514650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>579009</t>
+          <t>580231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,47 +5003,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3530061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>3532100</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3532100</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3444892</t>
+          <t>3440419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3613635</t>
+          <t>3614545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -5081,82 +5081,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3375601</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>3215</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>3377618</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3215</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3377618</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3296083</t>
+          <t>3295173</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3464826</t>
+          <t>3469299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2023</t>
+          <t>Sexo adulto elegido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,47 +5577,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>754492</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>755508</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1427</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>755508</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>728139</t>
+          <t>729180</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>786541</t>
+          <t>785965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -5655,82 +5655,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>513509</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>514938</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>514938</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>483905</t>
+          <t>484481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>542307</t>
+          <t>541266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,47 +5920,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2236352</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2921</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>2237823</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,93%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2921</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2237823</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1891929</t>
+          <t>1873364</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2510758</t>
+          <t>2518530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,62%</t>
         </is>
       </c>
     </row>
@@ -5998,82 +5998,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2288120</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>2290327</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1471</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2290327</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2017392</t>
+          <t>2009620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2636221</t>
+          <t>2654786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,47 +6263,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>659201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>660463</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>660463</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>621962</t>
+          <t>623180</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>698752</t>
+          <t>697610</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -6341,82 +6341,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>646623</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>646623</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>608334</t>
+          <t>609476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685124</t>
+          <t>683906</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,47 +6606,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3652483</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>3653794</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,96%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>5352</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3653794</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3270995</t>
+          <t>3250285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3932773</t>
+          <t>3950348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -6684,82 +6684,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3449919</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>3364</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>3451889</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3364</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3451889</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3172910</t>
+          <t>3155335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3834688</t>
+          <t>3855398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/SE_ADU-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/SE_ADU-Estudios-trans_orig.xlsx
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1270291</t>
+          <t>1262767</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1361093</t>
+          <t>1358523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>985742</t>
+          <t>988312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1076544</t>
+          <t>1084068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1529902</t>
+          <t>1527931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1642952</t>
+          <t>1646965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,2%</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1638134</t>
+          <t>1634121</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1751184</t>
+          <t>1753155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>442829</t>
+          <t>444172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>508772</t>
+          <t>509620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519048</t>
+          <t>518200</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584991</t>
+          <t>583648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3299502</t>
+          <t>3291559</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3461675</t>
+          <t>3465110</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3194066</t>
+          <t>3190631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3356239</t>
+          <t>3364182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1287723</t>
+          <t>1284551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1387762</t>
+          <t>1385274</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>924678</t>
+          <t>927166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1024717</t>
+          <t>1027889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1697545</t>
+          <t>1694165</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1827484</t>
+          <t>1819470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1894276</t>
+          <t>1902290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2024215</t>
+          <t>2027595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>429091</t>
+          <t>427271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>491266</t>
+          <t>492075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>448547</t>
+          <t>447738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>510722</t>
+          <t>512542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,54%</t>
         </is>
       </c>
     </row>
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3465078</t>
+          <t>3473432</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3645944</t>
+          <t>3647814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3328068</t>
+          <t>3326198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3508934</t>
+          <t>3500580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>950138</t>
+          <t>952025</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1033460</t>
+          <t>1033409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>715547</t>
+          <t>715598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>798869</t>
+          <t>796982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1922389</t>
+          <t>1919643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2052613</t>
+          <t>2052864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2012072</t>
+          <t>2011821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2142296</t>
+          <t>2145042</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>515796</t>
+          <t>511575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>581377</t>
+          <t>580568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>514650</t>
+          <t>515459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>580231</t>
+          <t>584452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3440419</t>
+          <t>3447829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3614545</t>
+          <t>3606773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3295173</t>
+          <t>3302945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3469299</t>
+          <t>3461889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>729180</t>
+          <t>790460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>785965</t>
+          <t>855625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>484481</t>
+          <t>544942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>541266</t>
+          <t>610107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1873364</t>
+          <t>2100565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2518530</t>
+          <t>2239933</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230567</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2009620</t>
+          <t>2162026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2654786</t>
+          <t>2301394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>623180</t>
+          <t>696896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>697610</t>
+          <t>772946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609476</t>
+          <t>673518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>683906</t>
+          <t>749568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3250285</t>
+          <t>3642690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3950348</t>
+          <t>3813370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3155335</t>
+          <t>3435620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3855398</t>
+          <t>3606300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
